--- a/backend/data/financials_by_company/1442.HK.xlsx
+++ b/backend/data/financials_by_company/1442.HK.xlsx
@@ -3995,10 +3995,8 @@
           <t>Pulau Indah</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>42920</t>
-        </is>
+      <c r="D2" t="n">
+        <v>42920</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4212,7 +4210,7 @@
         <v>-5093000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>1.95</v>
@@ -4389,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>0.0467</v>
